--- a/data/2026/08-brasov/40198-brasov/budget_file.xlsx
+++ b/data/2026/08-brasov/40198-brasov/budget_file.xlsx
@@ -7236,7 +7236,7 @@
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>66.02 total_2026: parent 0,00 != sum(children) 20.651,00 (1 children); 66.02 credite_angajament: parent 0,00 != sum(children) 25.650,00 (1 children)</t>
+          <t>66.02 credite_angajament: parent 0,00 != sum(children) 25.650,00 (1 children); 66.02 total_2026: parent 0,00 != sum(children) 20.651,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="M165" s="4" t="inlineStr">
         <is>
-          <t>71 total_2026: parent 0,00 != sum(children) 20.651,00 (1 children); 71 credite_angajament: parent 0,00 != sum(children) 25.650,00 (1 children)</t>
+          <t>71 credite_angajament: parent 0,00 != sum(children) 25.650,00 (1 children); 71 total_2026: parent 0,00 != sum(children) 20.651,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="M172" s="4" t="inlineStr">
         <is>
-          <t>67.02 est2027: parent 48.882,59 != sum(children) 48.072,59 (2 children); 67.02 total_2026: parent 61.796,73 != sum(children) 56.371,23 (2 children); 67.02 credite_angajament: parent 144.419,25 != sum(children) 138.183,75 (2 children)</t>
+          <t>67.02 credite_angajament: parent 144.419,25 != sum(children) 138.183,75 (2 children); 67.02 total_2026: parent 61.796,73 != sum(children) 56.371,23 (2 children); 67.02 est2027: parent 48.882,59 != sum(children) 48.072,59 (2 children)</t>
         </is>
       </c>
     </row>
@@ -13400,7 +13400,7 @@
       </c>
       <c r="M309" s="4" t="inlineStr">
         <is>
-          <t>98.02 est2029: parent 0,00 != sum(children) 391.004,00 (1 children); 98.02 est2028: parent 0,00 != sum(children) 371.363,00 (1 children); 98.02 est2027: parent 0,00 != sum(children) 255.247,86 (1 children)</t>
+          <t>98.02 est2027: parent 0,00 != sum(children) 255.247,86 (1 children); 98.02 est2029: parent 0,00 != sum(children) 391.004,00 (1 children); 98.02 est2028: parent 0,00 != sum(children) 371.363,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -17956,7 +17956,7 @@
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 0,00 != sum(children) 315.652,26 (12 children); 01 credite_angajament: parent 0,00 != sum(children) 29.703,00 (12 children)</t>
+          <t>01 credite_angajament: parent 0,00 != sum(children) 29.703,00 (12 children); 01 total_2026: parent 0,00 != sum(children) 315.652,26 (12 children)</t>
         </is>
       </c>
     </row>
@@ -28708,47 +28708,51 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
+      <c r="A356" s="4" t="inlineStr">
         <is>
           <t>20.01.08</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B356" s="4" t="inlineStr">
         <is>
           <t>61.02</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
+      <c r="C356" s="4" t="inlineStr">
         <is>
           <t>Posta, telecomunicatii, radio, tv, internet</t>
         </is>
       </c>
-      <c r="E356" t="n">
+      <c r="D356" s="4" t="n"/>
+      <c r="E356" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G356" s="3" t="n">
+      <c r="F356" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G356" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="H356" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I356" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J356" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K356" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L356" t="inlineStr">
+      <c r="H356" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I356" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" s="5" t="n"/>
+      <c r="K356" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L356" s="4" t="inlineStr">
         <is>
           <t>ocr</t>
+        </is>
+      </c>
+      <c r="M356" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell '0,00 0,00' in column est2029</t>
         </is>
       </c>
     </row>
@@ -30154,7 +30158,7 @@
       </c>
       <c r="M388" s="4" t="inlineStr">
         <is>
-          <t>65.02 total_2026: parent 248.224,39 != sum(children) 168.274,24 (2 children); 65.02 credite_angajament: parent 445.460,24 != sum(children) 73.362,09 (2 children)</t>
+          <t>65.02 credite_angajament: parent 445.460,24 != sum(children) 73.362,09 (2 children); 65.02 total_2026: parent 248.224,39 != sum(children) 168.274,24 (2 children)</t>
         </is>
       </c>
     </row>
@@ -34883,7 +34887,7 @@
       </c>
       <c r="M498" s="4" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 0,00 != sum(children) 181.761,48 (5 children); 01 est2028: parent 217.240,93 != sum(children) 198.304,00 (5 children); 01 est2027: parent 221.560,59 != sum(children) 200.505,00 (5 children)</t>
+          <t>01 est2027: parent 221.560,59 != sum(children) 200.505,00 (5 children); 01 total_2026: parent 0,00 != sum(children) 181.761,48 (5 children); 01 est2028: parent 217.240,93 != sum(children) 198.304,00 (5 children)</t>
         </is>
       </c>
     </row>
@@ -44083,7 +44087,7 @@
       </c>
       <c r="M709" s="4" t="inlineStr">
         <is>
-          <t>74.02 total_2026: parent 228.022,93 != sum(children) 199.312,20 (2 children); 74.02 credite_angajament: parent 238.076,70 != sum(children) 175.563,97 (2 children)</t>
+          <t>74.02 credite_angajament: parent 238.076,70 != sum(children) 175.563,97 (2 children); 74.02 total_2026: parent 228.022,93 != sum(children) 199.312,20 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44134,7 +44138,7 @@
       </c>
       <c r="M710" s="4" t="inlineStr">
         <is>
-          <t>01 est2027: parent 178.661,77 != sum(children) 103.207,80 (3 children); 01 total_2026: parent 199.312,20 != sum(children) 104.500,20 (3 children); 01 credite_angajament: parent 175.563,97 != sum(children) 5.298,00 (3 children)</t>
+          <t>01 credite_angajament: parent 175.563,97 != sum(children) 5.298,00 (3 children); 01 total_2026: parent 199.312,20 != sum(children) 104.500,20 (3 children); 01 est2027: parent 178.661,77 != sum(children) 103.207,80 (3 children)</t>
         </is>
       </c>
     </row>
@@ -46308,7 +46312,7 @@
       </c>
       <c r="M761" s="4" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 0,00 != sum(children) 285.071,44 (1 children); 84.02 credite_angajament: parent 0,00 != sum(children) 623.190,32 (1 children); 84.02 total_2026: parent 0,00 != sum(children) 33.750,00 (3 children); 84.02 credite_angajament: parent 0,00 != sum(children) 512.071,86 (3 children)</t>
+          <t>84.02 credite_angajament: parent 0,00 != sum(children) 623.190,32 (1 children); 84.02 total_2026: parent 0,00 != sum(children) 285.071,44 (1 children); 84.02 credite_angajament: parent 0,00 != sum(children) 512.071,86 (3 children); 84.02 total_2026: parent 0,00 != sum(children) 33.750,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -50767,9 +50771,10 @@
       </c>
     </row>
     <row r="863">
-      <c r="C863" s="2">
-        <f>== SECTIUNEA FUNCTIONARE === ===============================</f>
-        <v/>
+      <c r="C863" s="2" t="inlineStr">
+        <is>
+          <t>=== SECTIUNEA FUNCTIONARE === ===============================</t>
+        </is>
       </c>
       <c r="E863" t="n">
         <v>30</v>
@@ -53746,7 +53751,7 @@
       </c>
       <c r="M937" s="4" t="inlineStr">
         <is>
-          <t>01 est2029: parent 1.026.511,00 != sum(children) 611.883,00 (7 children); 01 est2027: parent 991.956,80 != sum(children) 585.445,00 (7 children); 01 total_2026: parent 995.784,06 != sum(children) 600.284,42 (7 children); 01 est2028: parent 993.094,28 != sum(children) 584.801,00 (7 children)</t>
+          <t>01 est2028: parent 993.094,28 != sum(children) 584.801,00 (7 children); 01 est2029: parent 1.026.511,00 != sum(children) 611.883,00 (7 children); 01 total_2026: parent 995.784,06 != sum(children) 600.284,42 (7 children); 01 est2027: parent 991.956,80 != sum(children) 585.445,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -66818,7 +66823,7 @@
       </c>
       <c r="M1236" s="4" t="inlineStr">
         <is>
-          <t>67.02 est2029: parent 198.332,00 != sum(children) 193.955,00 (2 children); 67.02 est2027: parent 198.255,00 != sum(children) 193.880,00 (2 children); 67.02 total_2026: parent 196.026,98 != sum(children) 191.696,48 (2 children); 67.02 est2028: parent 198.304,00 != sum(children) 193.929,00 (2 children)</t>
+          <t>67.02 est2028: parent 198.304,00 != sum(children) 193.929,00 (2 children); 67.02 est2029: parent 198.332,00 != sum(children) 193.955,00 (2 children); 67.02 total_2026: parent 196.026,98 != sum(children) 191.696,48 (2 children); 67.02 est2027: parent 198.255,00 != sum(children) 193.880,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -69171,7 +69176,7 @@
       </c>
       <c r="M1289" s="4" t="inlineStr">
         <is>
-          <t>67.02.05 est2029: parent 120.951,00 != sum(children) 82.715,00 (2 children); 67.02.05 est2027: parent 120.901,00 != sum(children) 82.682,00 (2 children); 67.02.05 total_2026: parent 119.347,80 != sum(children) 81.513,80 (2 children); 67.02.05 est2028: parent 120.934,00 != sum(children) 82.704,00 (2 children)</t>
+          <t>67.02.05 est2028: parent 120.934,00 != sum(children) 82.704,00 (2 children); 67.02.05 est2029: parent 120.951,00 != sum(children) 82.715,00 (2 children); 67.02.05 total_2026: parent 119.347,80 != sum(children) 81.513,80 (2 children); 67.02.05 est2027: parent 120.901,00 != sum(children) 82.682,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -77016,7 +77021,7 @@
       </c>
       <c r="M1472" s="4" t="inlineStr">
         <is>
-          <t>84.02.03 est2029: parent 245.684,00 != sum(children) 117.890,00 (1 children); 84.02.03 est2027: parent 198.277,00 != sum(children) 90.535,00 (1 children); 84.02.03 total_2026: parent 180.493,00 != sum(children) 88.767,00 (1 children); 84.02.03 est2028: parent 198.089,00 != sum(children) 90.315,00 (1 children)</t>
+          <t>84.02.03 est2028: parent 198.089,00 != sum(children) 90.315,00 (1 children); 84.02.03 est2029: parent 245.684,00 != sum(children) 117.890,00 (1 children); 84.02.03 total_2026: parent 180.493,00 != sum(children) 88.767,00 (1 children); 84.02.03 est2027: parent 198.277,00 != sum(children) 90.535,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -78314,7 +78319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -78513,12 +78518,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>credite_angajament</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 0,00 != sum(children) 315.652,26 (12 children)</t>
+          <t>01 credite_angajament: parent 0,00 != sum(children) 29.703,00 (12 children)</t>
         </is>
       </c>
     </row>
@@ -78543,12 +78548,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>credite_angajament</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01 credite_angajament: parent 0,00 != sum(children) 29.703,00 (12 children)</t>
+          <t>01 total_2026: parent 0,00 != sum(children) 315.652,26 (12 children)</t>
         </is>
       </c>
     </row>
@@ -78765,7 +78770,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -78774,21 +78779,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
+        <v>13</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.02 total_2026: parent 248.224,39 != sum(children) 168.274,24 (2 children)</t>
+          <t>unparseable cell '0,00 0,00' in column est2029</t>
         </is>
       </c>
     </row>
@@ -78838,7 +78838,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -78848,7 +78848,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 168.274,24 != sum(children) 13.558,90 (7 children)</t>
+          <t>65.02 total_2026: parent 248.224,39 != sum(children) 168.274,24 (2 children)</t>
         </is>
       </c>
     </row>
@@ -78868,7 +78868,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -78878,7 +78878,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10 total_2026: parent 13.558,90 != sum(children) 12.979,01 (3 children)</t>
+          <t>01 total_2026: parent 168.274,24 != sum(children) 13.558,90 (7 children)</t>
         </is>
       </c>
     </row>
@@ -78894,11 +78894,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -78908,7 +78908,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 0,00 != sum(children) 181.761,48 (5 children)</t>
+          <t>10 total_2026: parent 13.558,90 != sum(children) 12.979,01 (3 children)</t>
         </is>
       </c>
     </row>
@@ -78933,12 +78933,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>01 est2028: parent 217.240,93 != sum(children) 198.304,00 (5 children)</t>
+          <t>01 est2027: parent 221.560,59 != sum(children) 200.505,00 (5 children)</t>
         </is>
       </c>
     </row>
@@ -78963,12 +78963,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>01 est2027: parent 221.560,59 != sum(children) 200.505,00 (5 children)</t>
+          <t>01 total_2026: parent 0,00 != sum(children) 181.761,48 (5 children)</t>
         </is>
       </c>
     </row>
@@ -78988,17 +78988,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10.03 total_2026: parent 0,00 != sum(children) 116,00 (1 children)</t>
+          <t>01 est2028: parent 217.240,93 != sum(children) 198.304,00 (5 children)</t>
         </is>
       </c>
     </row>
@@ -79014,11 +79014,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -79028,7 +79028,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 0,00 != sum(children) 142.751,40 (6 children)</t>
+          <t>10.03 total_2026: parent 0,00 != sum(children) 116,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -79058,7 +79058,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 0,00 != sum(children) 142.751,40 (2 children)</t>
+          <t>68.02 total_2026: parent 0,00 != sum(children) 142.751,40 (6 children)</t>
         </is>
       </c>
     </row>
@@ -79074,21 +79074,21 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>credite_angajament</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.02 credite_angajament: parent 0,00 != sum(children) 249.278,86 (4 children)</t>
+          <t>68.02 total_2026: parent 0,00 != sum(children) 142.751,40 (2 children)</t>
         </is>
       </c>
     </row>
@@ -79118,7 +79118,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.02 credite_angajament: parent 0,00 != sum(children) 249.278,86 (3 children)</t>
+          <t>70.02 credite_angajament: parent 0,00 != sum(children) 249.278,86 (4 children)</t>
         </is>
       </c>
     </row>
@@ -79134,21 +79134,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>credite_angajament</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>74.02 total_2026: parent 228.022,93 != sum(children) 199.312,20 (2 children)</t>
+          <t>70.02 credite_angajament: parent 0,00 != sum(children) 249.278,86 (3 children)</t>
         </is>
       </c>
     </row>
@@ -79198,17 +79198,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>01 est2027: parent 178.661,77 != sum(children) 103.207,80 (3 children)</t>
+          <t>74.02 total_2026: parent 228.022,93 != sum(children) 199.312,20 (2 children)</t>
         </is>
       </c>
     </row>
@@ -79233,12 +79233,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>credite_angajament</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 199.312,20 != sum(children) 104.500,20 (3 children)</t>
+          <t>01 credite_angajament: parent 175.563,97 != sum(children) 5.298,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -79263,12 +79263,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>credite_angajament</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01 credite_angajament: parent 175.563,97 != sum(children) 5.298,00 (3 children)</t>
+          <t>01 total_2026: parent 199.312,20 != sum(children) 104.500,20 (3 children)</t>
         </is>
       </c>
     </row>
@@ -79288,17 +79288,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>55.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>55.01 total_2026: parent 4.176,20 != sum(children) 2.858,00 (1 children)</t>
+          <t>01 est2027: parent 178.661,77 != sum(children) 103.207,80 (3 children)</t>
         </is>
       </c>
     </row>
@@ -79314,11 +79314,11 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>55.01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -79328,7 +79328,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 0,00 != sum(children) 285.071,44 (1 children)</t>
+          <t>55.01 total_2026: parent 4.176,20 != sum(children) 2.858,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -79388,7 +79388,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 0,00 != sum(children) 33.750,00 (3 children)</t>
+          <t>84.02 total_2026: parent 0,00 != sum(children) 285.071,44 (1 children)</t>
         </is>
       </c>
     </row>
@@ -79425,62 +79425,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>00.02</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>duplicate of p30 with different values</t>
+          <t>84.02 total_2026: parent 0,00 != sum(children) 33.750,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>16.02.03</t>
+          <t>00.02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>rând absent, derivat aritmetic din formula părintelui 16.02</t>
+          <t>duplicate of p30 with different values</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -79493,37 +79498,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (41%): '(rând derivat din formula tipărită)' vs 'Taxe si tarife pentru eliberarea de lice'</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 16.02</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>50.02</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>16.02.03</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>50.02 total_2026: parent 1.006.716,06 != sum(children) 995.784,06 (2 children)</t>
+          <t>name mismatch vs nomenclator (41%): '(rând derivat din formula tipărită)' vs 'Taxe si tarife pentru eliberarea de lice'</t>
         </is>
       </c>
     </row>
@@ -79543,17 +79543,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>est2029</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>01 est2029: parent 1.026.511,00 != sum(children) 611.883,00 (7 children)</t>
+          <t>50.02 total_2026: parent 1.006.716,06 != sum(children) 995.784,06 (2 children)</t>
         </is>
       </c>
     </row>
@@ -79578,12 +79578,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>01 est2027: parent 991.956,80 != sum(children) 585.445,00 (7 children)</t>
+          <t>01 est2028: parent 993.094,28 != sum(children) 584.801,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -79608,12 +79608,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 995.784,06 != sum(children) 600.284,42 (7 children)</t>
+          <t>01 est2029: parent 1.026.511,00 != sum(children) 611.883,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -79638,12 +79638,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>01 est2028: parent 993.094,28 != sum(children) 584.801,00 (7 children)</t>
+          <t>01 total_2026: parent 995.784,06 != sum(children) 600.284,42 (7 children)</t>
         </is>
       </c>
     </row>
@@ -79663,17 +79663,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10.03 total_2026: parent 3.248,89 != sum(children) 10,00 (5 children)</t>
+          <t>01 est2027: parent 991.956,80 != sum(children) 585.445,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -79689,11 +79689,11 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -79703,7 +79703,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 0,00 != sum(children) 25.789,00 (3 children)</t>
+          <t>10.03 total_2026: parent 3.248,89 != sum(children) 10,00 (5 children)</t>
         </is>
       </c>
     </row>
@@ -79719,11 +79719,11 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -79733,7 +79733,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>59 total_2026: parent 5.116,00 != sum(children) 553,00 (1 children)</t>
+          <t>01 total_2026: parent 0,00 != sum(children) 25.789,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -79749,11 +79749,11 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -79763,44 +79763,49 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 0,00 != sum(children) 4.113,50 (3 children)</t>
+          <t>59 total_2026: parent 5.116,00 != sum(children) 553,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10.03.05</t>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (46%): 'Prie pe poe de de de de dase de dgat' vs 'Prime de asigurare viata platite de anga'</t>
+          <t>01 total_2026: parent 0,00 != sum(children) 4.113,50 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -79808,17 +79813,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>10.03.05</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20 total_2026: parent 1.248,50 != sum(children) 1.192,00 (6 children)</t>
+          <t>name mismatch vs nomenclator (46%): 'Prie pe poe de de de de dase de dgat' vs 'Prime de asigurare viata platite de anga'</t>
         </is>
       </c>
     </row>
@@ -79834,11 +79834,11 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -79848,7 +79848,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>66.02 total_2026: parent 0,00 != sum(children) 13.219,00 (1 children)</t>
+          <t>20 total_2026: parent 1.248,50 != sum(children) 1.192,00 (6 children)</t>
         </is>
       </c>
     </row>
@@ -79868,7 +79868,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -79878,7 +79878,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 0,00 != sum(children) 287,00 (2 children)</t>
+          <t>66.02 total_2026: parent 0,00 != sum(children) 13.219,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -79894,21 +79894,21 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>est2029</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>67.02 est2029: parent 198.332,00 != sum(children) 193.955,00 (2 children)</t>
+          <t>01 total_2026: parent 0,00 != sum(children) 287,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -79933,12 +79933,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>67.02 est2027: parent 198.255,00 != sum(children) 193.880,00 (2 children)</t>
+          <t>67.02 est2028: parent 198.304,00 != sum(children) 193.929,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -79963,12 +79963,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 196.026,98 != sum(children) 191.696,48 (2 children)</t>
+          <t>67.02 est2029: parent 198.332,00 != sum(children) 193.955,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -79993,12 +79993,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>67.02 est2028: parent 198.304,00 != sum(children) 193.929,00 (2 children)</t>
+          <t>67.02 total_2026: parent 196.026,98 != sum(children) 191.696,48 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80014,21 +80014,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>67.02.05</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>est2029</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>67.02.05 est2029: parent 120.951,00 != sum(children) 82.715,00 (2 children)</t>
+          <t>67.02 est2027: parent 198.255,00 != sum(children) 193.880,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80053,12 +80053,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>67.02.05 est2027: parent 120.901,00 != sum(children) 82.682,00 (2 children)</t>
+          <t>67.02.05 est2028: parent 120.934,00 != sum(children) 82.704,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80083,12 +80083,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>67.02.05 total_2026: parent 119.347,80 != sum(children) 81.513,80 (2 children)</t>
+          <t>67.02.05 est2029: parent 120.951,00 != sum(children) 82.715,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80113,12 +80113,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>67.02.05 est2028: parent 120.934,00 != sum(children) 82.704,00 (2 children)</t>
+          <t>67.02.05 total_2026: parent 119.347,80 != sum(children) 81.513,80 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80134,21 +80134,21 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>67.02.05</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 0,00 != sum(children) 90.340,40 (4 children)</t>
+          <t>67.02.05 est2027: parent 120.901,00 != sum(children) 82.682,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80168,7 +80168,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -80178,7 +80178,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20 total_2026: parent 0,00 != sum(children) 1.119,00 (8 children)</t>
+          <t>01 total_2026: parent 0,00 != sum(children) 90.340,40 (4 children)</t>
         </is>
       </c>
     </row>
@@ -80194,11 +80194,11 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -80208,7 +80208,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>70.02 total_2026: parent 69.636,00 != sum(children) 65.606,00 (2 children)</t>
+          <t>20 total_2026: parent 0,00 != sum(children) 1.119,00 (8 children)</t>
         </is>
       </c>
     </row>
@@ -80228,7 +80228,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -80238,7 +80238,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 65.606,00 != sum(children) 62.606,00 (3 children)</t>
+          <t>70.02 total_2026: parent 69.636,00 != sum(children) 65.606,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80254,11 +80254,11 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -80268,7 +80268,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 0,00 != sum(children) 180.493,00 (1 children)</t>
+          <t>01 total_2026: parent 65.606,00 != sum(children) 62.606,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -80298,7 +80298,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 0,00 != sum(children) 6.902,00 (2 children)</t>
+          <t>84.02 total_2026: parent 0,00 != sum(children) 180.493,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80318,7 +80318,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -80328,7 +80328,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>01 total_2026: parent 0,00 != sum(children) 173.013,00 (3 children)</t>
+          <t>84.02 total_2026: parent 0,00 != sum(children) 6.902,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80348,7 +80348,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -80358,7 +80358,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>10.03 total_2026: parent 0,00 != sum(children) 14,00 (1 children)</t>
+          <t>01 total_2026: parent 0,00 != sum(children) 173.013,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -80374,21 +80374,21 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>84.02.03</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>est2029</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>84.02.03 est2029: parent 245.684,00 != sum(children) 117.890,00 (1 children)</t>
+          <t>10.03 total_2026: parent 0,00 != sum(children) 14,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80413,12 +80413,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>84.02.03 est2027: parent 198.277,00 != sum(children) 90.535,00 (1 children)</t>
+          <t>84.02.03 est2028: parent 198.089,00 != sum(children) 90.315,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80443,12 +80443,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>84.02.03 total_2026: parent 180.493,00 != sum(children) 88.767,00 (1 children)</t>
+          <t>84.02.03 est2029: parent 245.684,00 != sum(children) 117.890,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80473,12 +80473,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>84.02.03 est2028: parent 198.089,00 != sum(children) 90.315,00 (1 children)</t>
+          <t>84.02.03 total_2026: parent 180.493,00 != sum(children) 88.767,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80494,21 +80494,21 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>84.02.03</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>42.02 total_2026: parent 0,00 != sum(children) 88.478,38 (6 children)</t>
+          <t>84.02.03 est2027: parent 198.277,00 != sum(children) 90.535,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80528,7 +80528,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>42.02.88</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -80538,7 +80538,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>42.02.88 total_2026: parent 0,00 != sum(children) 5.638,04 (4 children)</t>
+          <t>42.02 total_2026: parent 0,00 != sum(children) 88.478,38 (6 children)</t>
         </is>
       </c>
     </row>
@@ -80554,11 +80554,11 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>42.02.88</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -80568,7 +80568,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>66.02 total_2026: parent 0,00 != sum(children) 20.651,00 (1 children)</t>
+          <t>42.02.88 total_2026: parent 0,00 != sum(children) 5.638,04 (4 children)</t>
         </is>
       </c>
     </row>
@@ -80618,7 +80618,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -80628,7 +80628,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>71 total_2026: parent 0,00 != sum(children) 20.651,00 (1 children)</t>
+          <t>66.02 total_2026: parent 0,00 != sum(children) 20.651,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80674,21 +80674,21 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>67.02 est2027: parent 48.882,59 != sum(children) 48.072,59 (2 children)</t>
+          <t>71 total_2026: parent 0,00 != sum(children) 20.651,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80713,12 +80713,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>credite_angajament</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 61.796,73 != sum(children) 56.371,23 (2 children)</t>
+          <t>67.02 credite_angajament: parent 144.419,25 != sum(children) 138.183,75 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80743,12 +80743,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>credite_angajament</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>67.02 credite_angajament: parent 144.419,25 != sum(children) 138.183,75 (2 children)</t>
+          <t>67.02 total_2026: parent 61.796,73 != sum(children) 56.371,23 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80764,11 +80764,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -80778,7 +80778,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>74.02 est2027: parent 111.695,97 != sum(children) 77.893,97 (1 children)</t>
+          <t>67.02 est2027: parent 48.882,59 != sum(children) 48.072,59 (2 children)</t>
         </is>
       </c>
     </row>
@@ -80794,21 +80794,21 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>98.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>est2029</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>98.02 est2029: parent 0,00 != sum(children) 391.004,00 (1 children)</t>
+          <t>74.02 est2027: parent 111.695,97 != sum(children) 77.893,97 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80833,12 +80833,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>98.02 est2028: parent 0,00 != sum(children) 371.363,00 (1 children)</t>
+          <t>98.02 est2027: parent 0,00 != sum(children) 255.247,86 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80863,19 +80863,19 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>98.02 est2027: parent 0,00 != sum(children) 255.247,86 (1 children)</t>
+          <t>98.02 est2029: parent 0,00 != sum(children) 391.004,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -80884,7 +80884,12 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>98.02</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -80893,7 +80898,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>unparseable cell 'Sefserviciu,' in column est2028</t>
+          <t>98.02 est2028: parent 0,00 != sum(children) 371.363,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -80917,6 +80922,31 @@
         </is>
       </c>
       <c r="F88" t="inlineStr">
+        <is>
+          <t>unparseable cell 'Sefserviciu,' in column est2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>63</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>est2028</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>unparseable cell 'MariaOprea' in column est2028</t>
         </is>
@@ -80933,7 +80963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -80955,7 +80985,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -80965,60 +80995,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1751</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1698</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>96.90000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6685</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6470</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>96.90000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>33392de38e42ae0e9b673d09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>b199237dfa6815501d94bde880e1e696737983820d7c525066c710eea7b5956c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL LOCAL DETALIAT LA VENITURI PE CAPITOLE SI SUBCAPITOL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-63, 1812 linii</t>
         </is>
